--- a/reports/China_2.1.2_top_export_partners_cols_reverse.xlsx
+++ b/reports/China_2.1.2_top_export_partners_cols_reverse.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="193">
   <si>
     <t>reporterDesc</t>
   </si>
@@ -950,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:NL14"/>
+  <dimension ref="A1:NL15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:376">
@@ -13651,6 +13651,92 @@
         <v>1329800911.818</v>
       </c>
     </row>
+    <row r="15" spans="1:376">
+      <c r="A15" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="X15">
+        <v>0.0007811725185239833</v>
+      </c>
+      <c r="AB15">
+        <v>0.1426902863642937</v>
+      </c>
+      <c r="CA15">
+        <v>0.002533115733608061</v>
+      </c>
+      <c r="CC15">
+        <v>0.02320855495462205</v>
+      </c>
+      <c r="CD15">
+        <v>0.002436315507237814</v>
+      </c>
+      <c r="CF15">
+        <v>0.1646261049837786</v>
+      </c>
+      <c r="CM15">
+        <v>0.3220615711169312</v>
+      </c>
+      <c r="CU15">
+        <v>0.002219894898835043</v>
+      </c>
+      <c r="CZ15">
+        <v>0.004811534350750789</v>
+      </c>
+      <c r="DJ15">
+        <v>0.2505875162923319</v>
+      </c>
+      <c r="DZ15">
+        <v>0.02462467285681372</v>
+      </c>
+      <c r="EG15">
+        <v>0.01252164949105158</v>
+      </c>
+      <c r="FF15">
+        <v>0.04689761093122144</v>
+      </c>
+      <c r="HC15">
+        <v>415367517.712</v>
+      </c>
+      <c r="HG15">
+        <v>75871729539</v>
+      </c>
+      <c r="JF15">
+        <v>1346916294.923</v>
+      </c>
+      <c r="JH15">
+        <v>12340526109.903</v>
+      </c>
+      <c r="JI15">
+        <v>1295445372.959</v>
+      </c>
+      <c r="JK15">
+        <v>87535512266.754</v>
+      </c>
+      <c r="JR15">
+        <v>171247595342.999</v>
+      </c>
+      <c r="JZ15">
+        <v>1180369523.819</v>
+      </c>
+      <c r="KE15">
+        <v>2558404235</v>
+      </c>
+      <c r="KO15">
+        <v>133243185268</v>
+      </c>
+      <c r="LE15">
+        <v>13093508791.542</v>
+      </c>
+      <c r="LL15">
+        <v>6658050998.242</v>
+      </c>
+      <c r="MK15">
+        <v>24936545740.154</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C1:GG1"/>
